--- a/tables/Table_S_mediation_PC1_PC2.xlsx
+++ b/tables/Table_S_mediation_PC1_PC2.xlsx
@@ -401,10 +401,10 @@
         <v>-0.00141415466834074</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00219529165309582</v>
+        <v>-0.00222057363668472</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000597685976723593</v>
+        <v>0.000623475241972387</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.000479431346055756</v>
+        <v>-0.000479431346055757</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00131956523076902</v>
+        <v>-0.00131873145839995</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0000833499821995413</v>
+        <v>-0.0000738615458651603</v>
       </c>
     </row>
     <row r="4">
@@ -435,10 +435,10 @@
         <v>-0.00189358601439649</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00263200664356323</v>
+        <v>-0.00264375191619802</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.000349487994691308</v>
+        <v>-0.000316571007843786</v>
       </c>
     </row>
     <row r="5">
@@ -449,13 +449,13 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>0.253186991459987</v>
+        <v>0.253186991459988</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0289956935541216</v>
+        <v>0.0143807128082978</v>
       </c>
       <c r="E5" t="n">
-        <v>1.71537245598454</v>
+        <v>1.78426679023555</v>
       </c>
     </row>
     <row r="6">
@@ -469,10 +469,10 @@
         <v>-0.00129292158079461</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0019406213350023</v>
+        <v>-0.00193119689657277</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000259972604939285</v>
+        <v>0.000227788463481684</v>
       </c>
     </row>
     <row r="7">
@@ -486,10 +486,10 @@
         <v>-0.000600664433601884</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00120238105409625</v>
+        <v>-0.0011669049101679</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0000710769082744053</v>
+        <v>-0.0000567219744344389</v>
       </c>
     </row>
     <row r="8">
@@ -503,10 +503,10 @@
         <v>-0.00189358601439649</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.00261758377627608</v>
+        <v>-0.00262006946872375</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.000375881434791332</v>
+        <v>-0.000344426568523923</v>
       </c>
     </row>
     <row r="9">
@@ -520,10 +520,10 @@
         <v>0.317210007380268</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0267693527590594</v>
+        <v>0.0380941761394238</v>
       </c>
       <c r="E9" t="n">
-        <v>1.23799767946355</v>
+        <v>1.21659644896212</v>
       </c>
     </row>
   </sheetData>
